--- a/Test/Test_MATERIAL_PRICES.xlsx
+++ b/Test/Test_MATERIAL_PRICES.xlsx
@@ -28,8 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -646,7 +647,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46288.4445006284</v>
+        <v>46288.4552607716</v>
       </c>
     </row>
     <row r="3">
@@ -679,7 +680,7 @@
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46288.44450665903</v>
+        <v>46288.45526598334</v>
       </c>
     </row>
     <row r="4">
@@ -712,7 +713,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46288.44450760978</v>
+        <v>46288.45526690934</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +746,7 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46288.44449753715</v>
+        <v>46288.45525741233</v>
       </c>
     </row>
     <row r="6">
@@ -778,7 +779,7 @@
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46288.44449753727</v>
+        <v>46288.45525741244</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +812,7 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46288.44449753738</v>
+        <v>46288.45525741255</v>
       </c>
     </row>
     <row r="8">
@@ -844,7 +845,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46288.44449753748</v>
+        <v>46288.45525741265</v>
       </c>
     </row>
     <row r="9">
@@ -877,7 +878,7 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46288.44449753757</v>
+        <v>46288.45525741274</v>
       </c>
     </row>
     <row r="10">
@@ -910,7 +911,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46288.44449753766</v>
+        <v>46288.45525741284</v>
       </c>
     </row>
     <row r="11">
@@ -943,7 +944,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46288.44449753776</v>
+        <v>46288.45525741293</v>
       </c>
     </row>
     <row r="12">
@@ -976,7 +977,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46288.44449846158</v>
+        <v>46288.45525836807</v>
       </c>
     </row>
     <row r="13">
@@ -1009,7 +1010,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46288.44449846193</v>
+        <v>46288.45525836841</v>
       </c>
     </row>
     <row r="14">
@@ -1042,7 +1043,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46288.44449946233</v>
+        <v>46288.45525945756</v>
       </c>
     </row>
     <row r="15">
@@ -1075,7 +1076,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>46288.44449946265</v>
+        <v>46288.45525945836</v>
       </c>
     </row>
     <row r="16">
@@ -1117,7 +1118,7 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>46288.44449946278</v>
+        <v>46288.45525945859</v>
       </c>
     </row>
     <row r="17">
@@ -1150,7 +1151,7 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>46288.44449946329</v>
+        <v>46288.45525945875</v>
       </c>
     </row>
     <row r="18">
@@ -1183,7 +1184,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>46288.4444994634</v>
+        <v>46288.45525945893</v>
       </c>
     </row>
     <row r="19">
@@ -1216,7 +1217,7 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>46288.44450062898</v>
+        <v>46288.45526077212</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1250,7 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>46288.44450062922</v>
+        <v>46288.45526077228</v>
       </c>
     </row>
     <row r="21">
@@ -1282,7 +1283,7 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>46288.44450062936</v>
+        <v>46288.45526077242</v>
       </c>
     </row>
     <row r="22">
@@ -1315,7 +1316,7 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>46288.44450062953</v>
+        <v>46288.45526077252</v>
       </c>
     </row>
     <row r="23">
@@ -1342,13 +1343,22 @@
       <c r="E23" t="n">
         <v>15.21</v>
       </c>
+      <c r="F23" t="n">
+        <v>77</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-61.79</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.8024675324675324</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>CA313212</t>
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>46288.4445006297</v>
+        <v>46288.45526077269</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1391,7 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>46288.44450062987</v>
+        <v>46288.45526077337</v>
       </c>
     </row>
     <row r="25">
@@ -1414,7 +1424,7 @@
         </is>
       </c>
       <c r="J25" s="7" t="n">
-        <v>46288.44450063006</v>
+        <v>46288.45526077352</v>
       </c>
     </row>
     <row r="26">
@@ -1447,7 +1457,7 @@
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>46288.44450176549</v>
+        <v>46288.45526183151</v>
       </c>
     </row>
     <row r="27">
@@ -1480,7 +1490,7 @@
         </is>
       </c>
       <c r="J27" s="7" t="n">
-        <v>46288.44450469202</v>
+        <v>46288.45526414073</v>
       </c>
     </row>
     <row r="28">
@@ -1513,7 +1523,7 @@
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>46288.44450469167</v>
+        <v>46288.45526414045</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1565,7 @@
         </is>
       </c>
       <c r="J29" s="7" t="n">
-        <v>46288.44451323684</v>
+        <v>46288.45527198926</v>
       </c>
     </row>
     <row r="30">
@@ -1588,7 +1598,7 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>46288.44450571184</v>
+        <v>46288.45526507787</v>
       </c>
     </row>
     <row r="31">
@@ -1621,7 +1631,7 @@
         </is>
       </c>
       <c r="J31" s="7" t="n">
-        <v>46288.44450665935</v>
+        <v>46288.4552659839</v>
       </c>
     </row>
     <row r="32">
@@ -1654,7 +1664,7 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>46288.44450878375</v>
+        <v>46288.45526782903</v>
       </c>
     </row>
     <row r="33">
@@ -1687,7 +1697,7 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>46288.44450878409</v>
+        <v>46288.45526782973</v>
       </c>
     </row>
     <row r="34">
@@ -1720,7 +1730,7 @@
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>46288.44450991685</v>
+        <v>46288.45526886142</v>
       </c>
     </row>
     <row r="35">
@@ -1753,7 +1763,7 @@
         </is>
       </c>
       <c r="J35" s="7" t="n">
-        <v>46288.4445099173</v>
+        <v>46288.45526886274</v>
       </c>
     </row>
     <row r="36">
@@ -1786,7 +1796,7 @@
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>46288.44450991744</v>
+        <v>46288.45526886328</v>
       </c>
     </row>
     <row r="37">
@@ -1819,7 +1829,7 @@
         </is>
       </c>
       <c r="J37" s="7" t="n">
-        <v>46288.44451227724</v>
+        <v>46288.45527104104</v>
       </c>
     </row>
     <row r="38">
@@ -1852,7 +1862,7 @@
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>46288.44451227754</v>
+        <v>46288.4552710413</v>
       </c>
     </row>
     <row r="39">
@@ -1885,7 +1895,7 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>46288.44451227769</v>
+        <v>46288.45527104141</v>
       </c>
     </row>
     <row r="40">
@@ -1918,7 +1928,7 @@
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>46288.44451227779</v>
+        <v>46288.45527104151</v>
       </c>
     </row>
     <row r="41">
@@ -1951,7 +1961,7 @@
         </is>
       </c>
       <c r="J41" s="7" t="n">
-        <v>46288.44451227791</v>
+        <v>46288.45527104159</v>
       </c>
     </row>
     <row r="42">
@@ -1984,7 +1994,7 @@
         </is>
       </c>
       <c r="J42" s="7" t="n">
-        <v>46288.44451227799</v>
+        <v>46288.45527104168</v>
       </c>
     </row>
     <row r="43">
@@ -2017,7 +2027,7 @@
         </is>
       </c>
       <c r="J43" s="7" t="n">
-        <v>46288.4445122781</v>
+        <v>46288.45527104176</v>
       </c>
     </row>
     <row r="44">
@@ -2050,7 +2060,7 @@
         </is>
       </c>
       <c r="J44" s="7" t="n">
-        <v>46288.44451227821</v>
+        <v>46288.45527104185</v>
       </c>
     </row>
     <row r="45">
@@ -2083,7 +2093,7 @@
         </is>
       </c>
       <c r="J45" s="7" t="n">
-        <v>46288.44451227832</v>
+        <v>46288.45527104194</v>
       </c>
     </row>
     <row r="46">
@@ -2116,7 +2126,7 @@
         </is>
       </c>
       <c r="J46" s="7" t="n">
-        <v>46288.44451227842</v>
+        <v>46288.45527104204</v>
       </c>
     </row>
     <row r="47">
@@ -2149,7 +2159,7 @@
         </is>
       </c>
       <c r="J47" s="7" t="n">
-        <v>46288.44451323634</v>
+        <v>46288.45527198871</v>
       </c>
     </row>
   </sheetData>
@@ -2365,7 +2375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2146"/>
+  <dimension ref="A1:H2179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -71658,6 +71668,1035 @@
         <v>14.8</v>
       </c>
       <c r="G2146" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2147" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2147" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>87501</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>3/4" POLYWASHER B.M.C. 504</t>
+        </is>
+      </c>
+      <c r="F2148" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G2148" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>260759</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>THERMOPLUS 600 X 1100MM K2 RADIATOR 6501</t>
+        </is>
+      </c>
+      <c r="F2149" t="n">
+        <v>142</v>
+      </c>
+      <c r="G2149" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>461713</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>TUCKS METAL SPEED PLUG 300S 4.5X35MM ZP TUB</t>
+        </is>
+      </c>
+      <c r="F2150" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="G2150" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>14560</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>3.0M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="F2151" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G2151" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2152" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2152" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2153" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2153" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2154" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2154" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2155" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2155" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2156" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2156" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2156" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2157" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2157" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2157" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2158" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2158" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2158" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2159" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2159" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2159" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2160" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2160" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2160" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>19/8/26</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>414138</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>SDS+ MASONRY DRILL BIT 12.0 X 450MM 4 CUTTER</t>
+        </is>
+      </c>
+      <c r="E2161" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="G2161" t="inlineStr">
+        <is>
+          <t>CA313212</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2162" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2162" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2162" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>16/7/26</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>45718</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>TRACER LASER MEASURE ALM100 ALM100 TRACER</t>
+        </is>
+      </c>
+      <c r="F2163" t="n">
+        <v>88.62</v>
+      </c>
+      <c r="G2163" t="inlineStr">
+        <is>
+          <t>LY203947</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>16/7/26</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>31438</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>SEWER GULLY GRID 160 X 160MM</t>
+        </is>
+      </c>
+      <c r="F2164" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G2164" t="inlineStr">
+        <is>
+          <t>LY203947</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2/9/26</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>52238</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>KRINO 10X210MM SDS BIT DISPLAY PACK</t>
+        </is>
+      </c>
+      <c r="F2165" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G2165" t="inlineStr">
+        <is>
+          <t>N751006</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2/9/26</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>56001</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>DEWALT SDS HAMMER BODY ONLY 18V DWDCH273N-XJ</t>
+        </is>
+      </c>
+      <c r="F2166" t="n">
+        <v>227.62</v>
+      </c>
+      <c r="G2166" t="inlineStr">
+        <is>
+          <t>N751006</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2/9/26</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>52239</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>KRINO 12X210MM SDS BIT DISPLAY PACK</t>
+        </is>
+      </c>
+      <c r="F2167" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G2167" t="inlineStr">
+        <is>
+          <t>N751006</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>25203</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>IRISH PORTLAND CEMENT 25KG</t>
+        </is>
+      </c>
+      <c r="F2168" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G2168" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>69649</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>RONSEAL MULTI PURPOSE FILLER 3101ML MEDIUM 33367</t>
+        </is>
+      </c>
+      <c r="F2169" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="G2169" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>81960</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>1/2" BSS HP BALLVALVE NYLON PISTON 101A</t>
+        </is>
+      </c>
+      <c r="F2170" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="G2170" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>82052</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>4" X 1/2 POLY FLOAT FOR BALLCOCK</t>
+        </is>
+      </c>
+      <c r="F2171" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G2171" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>83961</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>PLUMB CENTRE COMPRESSION 3/4" 350</t>
+        </is>
+      </c>
+      <c r="F2172" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="G2172" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>TITAN 45/30 PVC WATER TANK 27GAL AA03</t>
+        </is>
+      </c>
+      <c r="F2173" t="n">
+        <v>95.91</v>
+      </c>
+      <c r="G2173" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>85045</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>TITAN PVC LID FOR SLIM 60 TANK AC06</t>
+        </is>
+      </c>
+      <c r="F2174" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="G2174" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>87501</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>3/4" POLYWASHER B.M.C. 504</t>
+        </is>
+      </c>
+      <c r="F2175" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G2175" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>260759</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>THERMOPLUS 600 X 1100MM K2 RADIATOR 6501</t>
+        </is>
+      </c>
+      <c r="F2176" t="n">
+        <v>142</v>
+      </c>
+      <c r="G2176" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>461713</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>TUCKS METAL SPEED PLUG 300S 4.5X35MM ZP TUB</t>
+        </is>
+      </c>
+      <c r="F2177" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="G2177" t="inlineStr">
+        <is>
+          <t>RH593039</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>14560</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>3.0M 100X44 ROUGH WHITE DEAL FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="F2178" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G2178" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2179" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2179" t="inlineStr">
         <is>
           <t>RH593157</t>
         </is>

--- a/Test/Test_MATERIAL_PRICES.xlsx
+++ b/Test/Test_MATERIAL_PRICES.xlsx
@@ -28,9 +28,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -647,7 +646,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46288.4552607716</v>
+        <v>46290.40085803825</v>
       </c>
     </row>
     <row r="3">
@@ -680,7 +679,7 @@
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46288.45526598334</v>
+        <v>46290.40086840352</v>
       </c>
     </row>
     <row r="4">
@@ -713,7 +712,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46288.45526690934</v>
+        <v>46290.40087033123</v>
       </c>
     </row>
     <row r="5">
@@ -746,7 +745,7 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46288.45525741233</v>
+        <v>46290.40085172875</v>
       </c>
     </row>
     <row r="6">
@@ -779,7 +778,7 @@
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46288.45525741244</v>
+        <v>46290.40085172901</v>
       </c>
     </row>
     <row r="7">
@@ -812,7 +811,7 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46288.45525741255</v>
+        <v>46290.40085172926</v>
       </c>
     </row>
     <row r="8">
@@ -845,7 +844,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46288.45525741265</v>
+        <v>46290.40085172946</v>
       </c>
     </row>
     <row r="9">
@@ -878,7 +877,7 @@
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46288.45525741274</v>
+        <v>46290.40085172967</v>
       </c>
     </row>
     <row r="10">
@@ -911,7 +910,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46288.45525741284</v>
+        <v>46290.40085172987</v>
       </c>
     </row>
     <row r="11">
@@ -944,7 +943,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46288.45525741293</v>
+        <v>46290.40085173007</v>
       </c>
     </row>
     <row r="12">
@@ -977,7 +976,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46288.45525836807</v>
+        <v>46290.40085367142</v>
       </c>
     </row>
     <row r="13">
@@ -1010,7 +1009,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46288.45525836841</v>
+        <v>46290.40085367186</v>
       </c>
     </row>
     <row r="14">
@@ -1043,7 +1042,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46288.45525945756</v>
+        <v>46290.40085585081</v>
       </c>
     </row>
     <row r="15">
@@ -1076,7 +1075,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>46288.45525945836</v>
+        <v>46290.40085585127</v>
       </c>
     </row>
     <row r="16">
@@ -1118,7 +1117,7 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>46288.45525945859</v>
+        <v>46290.40085585152</v>
       </c>
     </row>
     <row r="17">
@@ -1151,7 +1150,7 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>46288.45525945875</v>
+        <v>46290.40085585188</v>
       </c>
     </row>
     <row r="18">
@@ -1184,7 +1183,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>46288.45525945893</v>
+        <v>46290.40085585212</v>
       </c>
     </row>
     <row r="19">
@@ -1217,7 +1216,7 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>46288.45526077212</v>
+        <v>46290.40085803895</v>
       </c>
     </row>
     <row r="20">
@@ -1250,7 +1249,7 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>46288.45526077228</v>
+        <v>46290.40085803944</v>
       </c>
     </row>
     <row r="21">
@@ -1283,7 +1282,7 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>46288.45526077242</v>
+        <v>46290.40085803966</v>
       </c>
     </row>
     <row r="22">
@@ -1316,7 +1315,7 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>46288.45526077252</v>
+        <v>46290.40085803987</v>
       </c>
     </row>
     <row r="23">
@@ -1358,7 +1357,7 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>46288.45526077269</v>
+        <v>46290.40085804009</v>
       </c>
     </row>
     <row r="24">
@@ -1391,7 +1390,7 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>46288.45526077337</v>
+        <v>46290.4008580403</v>
       </c>
     </row>
     <row r="25">
@@ -1424,7 +1423,7 @@
         </is>
       </c>
       <c r="J25" s="7" t="n">
-        <v>46288.45526077352</v>
+        <v>46290.4008580405</v>
       </c>
     </row>
     <row r="26">
@@ -1457,7 +1456,7 @@
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>46288.45526183151</v>
+        <v>46290.40086068924</v>
       </c>
     </row>
     <row r="27">
@@ -1490,7 +1489,7 @@
         </is>
       </c>
       <c r="J27" s="7" t="n">
-        <v>46288.45526414073</v>
+        <v>46290.40086453805</v>
       </c>
     </row>
     <row r="28">
@@ -1523,7 +1522,7 @@
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>46288.45526414045</v>
+        <v>46290.40086453762</v>
       </c>
     </row>
     <row r="29">
@@ -1565,7 +1564,7 @@
         </is>
       </c>
       <c r="J29" s="7" t="n">
-        <v>46288.45527198926</v>
+        <v>46290.40088067882</v>
       </c>
     </row>
     <row r="30">
@@ -1598,7 +1597,7 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>46288.45526507787</v>
+        <v>46290.40086648309</v>
       </c>
     </row>
     <row r="31">
@@ -1631,7 +1630,7 @@
         </is>
       </c>
       <c r="J31" s="7" t="n">
-        <v>46288.4552659839</v>
+        <v>46290.40086840417</v>
       </c>
     </row>
     <row r="32">
@@ -1664,7 +1663,7 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>46288.45526782903</v>
+        <v>46290.40087229344</v>
       </c>
     </row>
     <row r="33">
@@ -1697,7 +1696,7 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>46288.45526782973</v>
+        <v>46290.40087229393</v>
       </c>
     </row>
     <row r="34">
@@ -1730,7 +1729,7 @@
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>46288.45526886142</v>
+        <v>46290.40087426703</v>
       </c>
     </row>
     <row r="35">
@@ -1763,7 +1762,7 @@
         </is>
       </c>
       <c r="J35" s="7" t="n">
-        <v>46288.45526886274</v>
+        <v>46290.4008742675</v>
       </c>
     </row>
     <row r="36">
@@ -1796,7 +1795,7 @@
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>46288.45526886328</v>
+        <v>46290.4008742678</v>
       </c>
     </row>
     <row r="37">
@@ -1829,7 +1828,7 @@
         </is>
       </c>
       <c r="J37" s="7" t="n">
-        <v>46288.45527104104</v>
+        <v>46290.40087884414</v>
       </c>
     </row>
     <row r="38">
@@ -1862,7 +1861,7 @@
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>46288.4552710413</v>
+        <v>46290.40087884455</v>
       </c>
     </row>
     <row r="39">
@@ -1895,7 +1894,7 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>46288.45527104141</v>
+        <v>46290.40087884478</v>
       </c>
     </row>
     <row r="40">
@@ -1928,7 +1927,7 @@
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>46288.45527104151</v>
+        <v>46290.40087884499</v>
       </c>
     </row>
     <row r="41">
@@ -1961,7 +1960,7 @@
         </is>
       </c>
       <c r="J41" s="7" t="n">
-        <v>46288.45527104159</v>
+        <v>46290.4008788452</v>
       </c>
     </row>
     <row r="42">
@@ -1994,7 +1993,7 @@
         </is>
       </c>
       <c r="J42" s="7" t="n">
-        <v>46288.45527104168</v>
+        <v>46290.40087884546</v>
       </c>
     </row>
     <row r="43">
@@ -2027,7 +2026,7 @@
         </is>
       </c>
       <c r="J43" s="7" t="n">
-        <v>46288.45527104176</v>
+        <v>46290.40087884567</v>
       </c>
     </row>
     <row r="44">
@@ -2060,7 +2059,7 @@
         </is>
       </c>
       <c r="J44" s="7" t="n">
-        <v>46288.45527104185</v>
+        <v>46290.40087884587</v>
       </c>
     </row>
     <row r="45">
@@ -2093,7 +2092,7 @@
         </is>
       </c>
       <c r="J45" s="7" t="n">
-        <v>46288.45527104194</v>
+        <v>46290.40087884609</v>
       </c>
     </row>
     <row r="46">
@@ -2126,7 +2125,7 @@
         </is>
       </c>
       <c r="J46" s="7" t="n">
-        <v>46288.45527104204</v>
+        <v>46290.4008788463</v>
       </c>
     </row>
     <row r="47">
@@ -2159,7 +2158,7 @@
         </is>
       </c>
       <c r="J47" s="7" t="n">
-        <v>46288.45527198871</v>
+        <v>46290.40088067839</v>
       </c>
     </row>
   </sheetData>
@@ -2375,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2179"/>
+  <dimension ref="A1:H2181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72697,6 +72696,72 @@
         <v>14.8</v>
       </c>
       <c r="G2179" t="inlineStr">
+        <is>
+          <t>RH593157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2180" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G2180" t="inlineStr">
+        <is>
+          <t>CA315587</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>30/6/26</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>OSB3 2440 X 590 X 18MM T&amp;G4 FSC Mix 70% NQA-COC-006596</t>
+        </is>
+      </c>
+      <c r="E2181" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="F2181" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G2181" t="inlineStr">
         <is>
           <t>RH593157</t>
         </is>
